--- a/shared/N_protein_metadata.xlsx
+++ b/shared/N_protein_metadata.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/charligeer/Documents/Lab_Projects/Repos/Bunya-50-N-experiments-update/shared/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/charligeer/Documents/Lab_Projects/Repos/Bunya-50-N-experiments/shared/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734DD60A-115F-1148-A363-B7B798FF6BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77B96FC-8EF7-344A-ADEA-2C03479491D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17240" xr2:uid="{109C7BF4-0B70-984C-89AA-119A886AE052}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="558">
   <si>
     <t>pMDS</t>
   </si>
@@ -642,9 +642,6 @@
   </si>
   <si>
     <t>10.3201/eid2103.141351</t>
-  </si>
-  <si>
-    <t>nsSNPs?</t>
   </si>
   <si>
     <t>KKV</t>
@@ -2188,7 +2185,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA618E13-A19F-4F46-8CDB-47B64397CFFD}">
-  <dimension ref="A1:U100"/>
+  <dimension ref="A1:T100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.33203125" style="9" customWidth="1"/>
@@ -2206,11 +2203,10 @@
     <col min="13" max="13" width="12.5" customWidth="1"/>
     <col min="14" max="14" width="17.33203125" customWidth="1"/>
     <col min="16" max="18" width="11.83203125" customWidth="1"/>
-    <col min="19" max="19" width="8" customWidth="1"/>
-    <col min="20" max="20" width="10.83203125" style="15"/>
+    <col min="19" max="19" width="10.83203125" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2224,7 +2220,7 @@
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>186</v>
@@ -2236,7 +2232,7 @@
         <v>3</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>4</v>
@@ -2260,22 +2256,19 @@
         <v>184</v>
       </c>
       <c r="Q1" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="S1" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="T1" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="T1" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" s="13">
         <v>59</v>
       </c>
@@ -2292,7 +2285,7 @@
         <v>180</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G2" s="9">
         <v>62.231999999999999</v>
@@ -2325,19 +2318,16 @@
         <v>185</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T2" s="18" t="s">
+        <v>475</v>
+      </c>
+      <c r="S2" s="18" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="13">
         <v>60</v>
       </c>
@@ -2354,7 +2344,7 @@
         <v>180</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G3" s="9">
         <v>66.524000000000001</v>
@@ -2387,19 +2377,16 @@
         <v>190</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T3" s="18" t="s">
+        <v>475</v>
+      </c>
+      <c r="S3" s="18" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="13">
         <v>61</v>
       </c>
@@ -2449,19 +2436,16 @@
         <v>193</v>
       </c>
       <c r="Q4" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="S4" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T4" s="18" t="s">
+        <v>475</v>
+      </c>
+      <c r="S4" s="18" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="13">
         <v>62</v>
       </c>
@@ -2478,7 +2462,7 @@
         <v>179</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G5" s="9">
         <v>68.67</v>
@@ -2511,19 +2495,16 @@
         <v>197</v>
       </c>
       <c r="Q5" t="s">
+        <v>476</v>
+      </c>
+      <c r="R5" t="s">
         <v>477</v>
       </c>
-      <c r="R5" t="s">
-        <v>478</v>
-      </c>
-      <c r="S5" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T5" s="18" t="s">
+      <c r="S5" s="18" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
         <v>63</v>
       </c>
@@ -2540,7 +2521,7 @@
         <v>180</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G6" s="9">
         <v>46.351999999999997</v>
@@ -2555,7 +2536,7 @@
         <v>44.634999999999998</v>
       </c>
       <c r="K6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L6" s="5" t="s">
         <v>25</v>
@@ -2567,25 +2548,22 @@
         <v>27</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="P6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q6" t="s">
+        <v>478</v>
+      </c>
+      <c r="R6" t="s">
         <v>479</v>
       </c>
-      <c r="R6" t="s">
-        <v>480</v>
-      </c>
-      <c r="S6" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T6" s="18" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S6" s="18" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" s="13">
         <v>64</v>
       </c>
@@ -2602,7 +2580,7 @@
         <v>179</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G7" s="9">
         <v>45.923000000000002</v>
@@ -2617,7 +2595,7 @@
         <v>43.347999999999999</v>
       </c>
       <c r="K7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>30</v>
@@ -2629,25 +2607,22 @@
         <v>31</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P7" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>480</v>
+      </c>
+      <c r="R7" t="s">
+        <v>481</v>
+      </c>
+      <c r="S7" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="Q7" t="s">
-        <v>481</v>
-      </c>
-      <c r="R7" t="s">
-        <v>482</v>
-      </c>
-      <c r="S7" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T7" s="18" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="13">
         <v>65</v>
       </c>
@@ -2664,7 +2639,7 @@
         <v>179</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G8" s="9">
         <v>44.872</v>
@@ -2679,7 +2654,7 @@
         <v>44.017000000000003</v>
       </c>
       <c r="K8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>34</v>
@@ -2691,25 +2666,22 @@
         <v>36</v>
       </c>
       <c r="O8" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="P8" t="s">
         <v>218</v>
       </c>
-      <c r="P8" t="s">
-        <v>219</v>
-      </c>
       <c r="Q8" t="s">
+        <v>482</v>
+      </c>
+      <c r="R8" t="s">
         <v>483</v>
       </c>
-      <c r="R8" t="s">
-        <v>484</v>
-      </c>
-      <c r="S8" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T8" s="18" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S8" s="18" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="13">
         <v>66</v>
       </c>
@@ -2726,7 +2698,7 @@
         <v>179</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G9" s="9">
         <v>46.351999999999997</v>
@@ -2741,7 +2713,7 @@
         <v>43.777000000000001</v>
       </c>
       <c r="K9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>38</v>
@@ -2753,25 +2725,22 @@
         <v>31</v>
       </c>
       <c r="O9" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="P9" t="s">
         <v>222</v>
       </c>
-      <c r="P9" t="s">
-        <v>223</v>
-      </c>
       <c r="Q9" t="s">
+        <v>484</v>
+      </c>
+      <c r="R9" t="s">
         <v>485</v>
       </c>
-      <c r="R9" t="s">
-        <v>486</v>
-      </c>
-      <c r="S9" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T9" s="18" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S9" s="18" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" s="13">
         <v>67</v>
       </c>
@@ -2788,7 +2757,7 @@
         <v>179</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G10" s="9">
         <v>43.161999999999999</v>
@@ -2803,7 +2772,7 @@
         <v>41.453000000000003</v>
       </c>
       <c r="K10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L10" s="5" t="s">
         <v>41</v>
@@ -2815,25 +2784,22 @@
         <v>44</v>
       </c>
       <c r="O10" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="P10" t="s">
         <v>224</v>
       </c>
-      <c r="P10" t="s">
-        <v>225</v>
-      </c>
       <c r="Q10" t="s">
+        <v>486</v>
+      </c>
+      <c r="R10" t="s">
         <v>487</v>
       </c>
-      <c r="R10" t="s">
-        <v>488</v>
-      </c>
-      <c r="S10" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T10" s="18" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S10" s="18" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="13">
         <v>68</v>
       </c>
@@ -2850,7 +2816,7 @@
         <v>180</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G11" s="9">
         <v>43.59</v>
@@ -2865,7 +2831,7 @@
         <v>41.453000000000003</v>
       </c>
       <c r="K11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L11" s="5" t="s">
         <v>47</v>
@@ -2877,25 +2843,22 @@
         <v>44</v>
       </c>
       <c r="O11" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="P11" t="s">
         <v>230</v>
       </c>
-      <c r="P11" t="s">
-        <v>231</v>
-      </c>
       <c r="Q11" t="s">
+        <v>488</v>
+      </c>
+      <c r="R11" t="s">
         <v>489</v>
       </c>
-      <c r="R11" t="s">
-        <v>490</v>
-      </c>
-      <c r="S11" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T11" s="18" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S11" s="18" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" s="13">
         <v>69</v>
       </c>
@@ -2912,7 +2875,7 @@
         <v>179</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G12" s="9">
         <v>44.872</v>
@@ -2927,7 +2890,7 @@
         <v>42.734999999999999</v>
       </c>
       <c r="K12" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L12" s="5" t="s">
         <v>50</v>
@@ -2939,25 +2902,22 @@
         <v>44</v>
       </c>
       <c r="O12" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="P12" t="s">
         <v>232</v>
       </c>
-      <c r="P12" t="s">
-        <v>233</v>
-      </c>
       <c r="Q12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="R12" t="s">
-        <v>372</v>
-      </c>
-      <c r="S12" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T12" s="18" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+        <v>371</v>
+      </c>
+      <c r="S12" s="18" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" s="13">
         <v>127</v>
       </c>
@@ -2974,7 +2934,7 @@
         <v>179</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G13" s="9">
         <v>71.674000000000007</v>
@@ -2989,7 +2949,7 @@
         <v>45.064</v>
       </c>
       <c r="K13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L13" s="5" t="s">
         <v>54</v>
@@ -3001,25 +2961,22 @@
         <v>55</v>
       </c>
       <c r="O13" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="P13" t="s">
         <v>240</v>
       </c>
-      <c r="P13" t="s">
-        <v>241</v>
-      </c>
       <c r="Q13" t="s">
+        <v>491</v>
+      </c>
+      <c r="R13" t="s">
         <v>492</v>
       </c>
-      <c r="R13" t="s">
-        <v>493</v>
-      </c>
-      <c r="S13" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T13" s="18" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S13" s="18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" s="13">
         <v>163</v>
       </c>
@@ -3036,7 +2993,7 @@
         <v>179</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G14" s="9">
         <v>35.744999999999997</v>
@@ -3051,7 +3008,7 @@
         <v>34.188000000000002</v>
       </c>
       <c r="K14" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L14" s="5" t="s">
         <v>58</v>
@@ -3063,25 +3020,22 @@
         <v>59</v>
       </c>
       <c r="O14" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="P14" t="s">
         <v>244</v>
       </c>
-      <c r="P14" t="s">
-        <v>245</v>
-      </c>
       <c r="Q14" t="s">
+        <v>493</v>
+      </c>
+      <c r="R14" t="s">
         <v>494</v>
       </c>
-      <c r="R14" t="s">
-        <v>495</v>
-      </c>
-      <c r="S14" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T14" s="18" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S14" s="18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" s="13">
         <v>164</v>
       </c>
@@ -3098,7 +3052,7 @@
         <v>180</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G15" s="9">
         <v>27.731000000000002</v>
@@ -3113,7 +3067,7 @@
         <v>31.933</v>
       </c>
       <c r="K15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>62</v>
@@ -3125,25 +3079,22 @@
         <v>64</v>
       </c>
       <c r="O15" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="P15" t="s">
         <v>249</v>
       </c>
-      <c r="P15" t="s">
-        <v>250</v>
-      </c>
       <c r="Q15" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="R15" s="6" t="s">
         <v>504</v>
       </c>
-      <c r="R15" s="6" t="s">
-        <v>505</v>
-      </c>
-      <c r="S15" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T15" s="18" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S15" s="18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" s="13">
         <v>165</v>
       </c>
@@ -3160,7 +3111,7 @@
         <v>179</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G16" s="9">
         <v>89.7</v>
@@ -3175,7 +3126,7 @@
         <v>39.055999999999997</v>
       </c>
       <c r="K16" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>67</v>
@@ -3187,25 +3138,22 @@
         <v>68</v>
       </c>
       <c r="O16" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="P16" t="s">
         <v>252</v>
       </c>
-      <c r="P16" t="s">
-        <v>253</v>
-      </c>
       <c r="Q16" t="s">
+        <v>495</v>
+      </c>
+      <c r="R16" t="s">
         <v>496</v>
       </c>
-      <c r="R16" t="s">
-        <v>497</v>
-      </c>
-      <c r="S16" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T16" s="18" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S16" s="18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" s="13">
         <v>166</v>
       </c>
@@ -3222,7 +3170,7 @@
         <v>180</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G17" s="9">
         <v>30.041</v>
@@ -3237,7 +3185,7 @@
         <v>31.405000000000001</v>
       </c>
       <c r="K17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>71</v>
@@ -3249,25 +3197,22 @@
         <v>72</v>
       </c>
       <c r="O17" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="P17" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>497</v>
+      </c>
+      <c r="R17" t="s">
+        <v>498</v>
+      </c>
+      <c r="S17" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="P17" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>498</v>
-      </c>
-      <c r="R17" t="s">
-        <v>499</v>
-      </c>
-      <c r="S17" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T17" s="16" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" s="13">
         <v>167</v>
       </c>
@@ -3284,7 +3229,7 @@
         <v>180</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G18" s="9">
         <v>90.558000000000007</v>
@@ -3299,7 +3244,7 @@
         <v>41.201999999999998</v>
       </c>
       <c r="K18" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L18" s="5" t="s">
         <v>75</v>
@@ -3311,25 +3256,22 @@
         <v>76</v>
       </c>
       <c r="O18" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="P18" t="s">
         <v>261</v>
       </c>
-      <c r="P18" t="s">
-        <v>262</v>
-      </c>
       <c r="Q18" t="s">
+        <v>499</v>
+      </c>
+      <c r="R18" t="s">
         <v>500</v>
       </c>
-      <c r="R18" t="s">
-        <v>501</v>
-      </c>
-      <c r="S18" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" s="11">
         <v>169</v>
       </c>
@@ -3337,7 +3279,7 @@
         <v>180</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>78</v>
@@ -3346,7 +3288,7 @@
         <v>180</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G19" s="9">
         <v>43.161999999999999</v>
@@ -3361,7 +3303,7 @@
         <v>41.88</v>
       </c>
       <c r="K19" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L19" s="5" t="s">
         <v>79</v>
@@ -3373,25 +3315,22 @@
         <v>44</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q19" t="s">
+        <v>501</v>
+      </c>
+      <c r="R19" t="s">
         <v>502</v>
       </c>
-      <c r="R19" t="s">
-        <v>503</v>
-      </c>
-      <c r="S19" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T19" s="18" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S19" s="18" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" s="11">
         <v>170</v>
       </c>
@@ -3408,7 +3347,7 @@
         <v>179</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G20" s="9">
         <v>41.201999999999998</v>
@@ -3435,25 +3374,22 @@
         <v>64</v>
       </c>
       <c r="O20" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="P20" t="s">
         <v>274</v>
       </c>
-      <c r="P20" t="s">
-        <v>275</v>
-      </c>
       <c r="Q20" t="s">
+        <v>277</v>
+      </c>
+      <c r="R20" t="s">
         <v>278</v>
       </c>
-      <c r="R20" t="s">
-        <v>279</v>
-      </c>
-      <c r="S20" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T20" s="15" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S20" s="15" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" s="11">
         <v>219</v>
       </c>
@@ -3470,7 +3406,7 @@
         <v>180</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G21" s="9">
         <v>100</v>
@@ -3497,25 +3433,22 @@
         <v>86</v>
       </c>
       <c r="O21" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="P21" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>282</v>
+      </c>
+      <c r="R21" t="s">
+        <v>283</v>
+      </c>
+      <c r="S21" s="18" t="s">
         <v>280</v>
       </c>
-      <c r="P21" t="s">
-        <v>287</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>283</v>
-      </c>
-      <c r="R21" t="s">
-        <v>284</v>
-      </c>
-      <c r="S21" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T21" s="18" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" s="11">
         <v>221</v>
       </c>
@@ -3532,7 +3465,7 @@
         <v>179</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G22" s="9">
         <v>93.132999999999996</v>
@@ -3547,7 +3480,7 @@
         <v>40.343000000000004</v>
       </c>
       <c r="K22" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L22" s="5" t="s">
         <v>89</v>
@@ -3559,25 +3492,22 @@
         <v>90</v>
       </c>
       <c r="O22" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="P22" t="s">
         <v>285</v>
       </c>
-      <c r="P22" t="s">
-        <v>286</v>
-      </c>
       <c r="Q22" t="s">
+        <v>288</v>
+      </c>
+      <c r="R22" t="s">
         <v>289</v>
       </c>
-      <c r="R22" t="s">
-        <v>290</v>
-      </c>
-      <c r="S22" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T22" s="18" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S22" s="18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" s="11">
         <v>222</v>
       </c>
@@ -3594,7 +3524,7 @@
         <v>179</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G23" s="9">
         <v>91.844999999999999</v>
@@ -3609,7 +3539,7 @@
         <v>40.773000000000003</v>
       </c>
       <c r="K23" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L23" s="5" t="s">
         <v>93</v>
@@ -3621,25 +3551,22 @@
         <v>94</v>
       </c>
       <c r="O23" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="P23" t="s">
         <v>293</v>
       </c>
-      <c r="P23" t="s">
+      <c r="Q23" t="s">
         <v>294</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="R23" t="s">
         <v>295</v>
       </c>
-      <c r="R23" t="s">
-        <v>296</v>
-      </c>
-      <c r="S23" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T23" s="18" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S23" s="18" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" s="11">
         <v>223</v>
       </c>
@@ -3656,7 +3583,7 @@
         <v>179</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G24" s="9">
         <v>87.123999999999995</v>
@@ -3671,7 +3598,7 @@
         <v>38.627000000000002</v>
       </c>
       <c r="K24" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L24" s="5" t="s">
         <v>97</v>
@@ -3683,25 +3610,22 @@
         <v>98</v>
       </c>
       <c r="O24" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="P24" t="s">
         <v>300</v>
       </c>
-      <c r="P24" t="s">
-        <v>301</v>
-      </c>
       <c r="Q24" t="s">
+        <v>304</v>
+      </c>
+      <c r="R24" t="s">
         <v>305</v>
       </c>
-      <c r="R24" t="s">
-        <v>306</v>
-      </c>
-      <c r="S24" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T24" s="18" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S24" s="18" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" s="11">
         <v>224</v>
       </c>
@@ -3718,7 +3642,7 @@
         <v>179</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G25" s="9">
         <v>92.275000000000006</v>
@@ -3733,7 +3657,7 @@
         <v>42.917999999999999</v>
       </c>
       <c r="K25" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>101</v>
@@ -3745,25 +3669,22 @@
         <v>98</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P25" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q25" t="s">
+        <v>308</v>
+      </c>
+      <c r="R25" t="s">
         <v>309</v>
       </c>
-      <c r="R25" t="s">
-        <v>310</v>
-      </c>
-      <c r="S25" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T25" s="18" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S25" s="18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" s="11">
         <v>225</v>
       </c>
@@ -3780,7 +3701,7 @@
         <v>180</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G26" s="9">
         <v>41.88</v>
@@ -3795,7 +3716,7 @@
         <v>43.59</v>
       </c>
       <c r="K26" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L26" s="5" t="s">
         <v>104</v>
@@ -3807,25 +3728,22 @@
         <v>44</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P26" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q26" t="s">
+        <v>315</v>
+      </c>
+      <c r="R26" t="s">
         <v>316</v>
       </c>
-      <c r="R26" t="s">
-        <v>317</v>
-      </c>
-      <c r="S26" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T26" s="15" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S26" s="15" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" s="11">
         <v>226</v>
       </c>
@@ -3842,7 +3760,7 @@
         <v>179</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G27" s="9">
         <v>44.872</v>
@@ -3857,7 +3775,7 @@
         <v>43.161999999999999</v>
       </c>
       <c r="K27" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L27" s="5" t="s">
         <v>107</v>
@@ -3869,28 +3787,25 @@
         <v>44</v>
       </c>
       <c r="O27" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="P27" t="s">
         <v>321</v>
       </c>
-      <c r="P27" t="s">
-        <v>322</v>
-      </c>
       <c r="Q27" t="s">
+        <v>323</v>
+      </c>
+      <c r="R27" t="s">
         <v>324</v>
       </c>
-      <c r="R27" t="s">
-        <v>325</v>
-      </c>
-      <c r="S27" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T27" s="15" t="s">
-        <v>331</v>
-      </c>
-      <c r="U27" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S27" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="T27" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" s="11">
         <v>227</v>
       </c>
@@ -3907,7 +3822,7 @@
         <v>179</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G28" s="9">
         <v>44.444000000000003</v>
@@ -3922,7 +3837,7 @@
         <v>42.308</v>
       </c>
       <c r="K28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L28" s="5" t="s">
         <v>110</v>
@@ -3934,28 +3849,25 @@
         <v>44</v>
       </c>
       <c r="O28" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="P28" t="s">
         <v>326</v>
       </c>
-      <c r="P28" t="s">
-        <v>327</v>
-      </c>
       <c r="Q28" t="s">
+        <v>328</v>
+      </c>
+      <c r="R28" t="s">
         <v>329</v>
       </c>
-      <c r="R28" t="s">
+      <c r="S28" s="15" t="s">
         <v>330</v>
       </c>
-      <c r="S28" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T28" s="15" t="s">
-        <v>331</v>
-      </c>
-      <c r="U28" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="T28" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" s="11">
         <v>228</v>
       </c>
@@ -3972,7 +3884,7 @@
         <v>179</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G29" s="9">
         <v>44.444000000000003</v>
@@ -3987,7 +3899,7 @@
         <v>43.161999999999999</v>
       </c>
       <c r="K29" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>113</v>
@@ -3999,28 +3911,25 @@
         <v>44</v>
       </c>
       <c r="O29" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="P29" t="s">
         <v>332</v>
       </c>
-      <c r="P29" t="s">
-        <v>333</v>
-      </c>
       <c r="Q29" t="s">
+        <v>334</v>
+      </c>
+      <c r="R29" t="s">
         <v>335</v>
       </c>
-      <c r="R29" t="s">
-        <v>336</v>
-      </c>
-      <c r="S29" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T29" s="15" t="s">
-        <v>331</v>
-      </c>
-      <c r="U29" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S29" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="T29" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" s="11">
         <v>229</v>
       </c>
@@ -4037,7 +3946,7 @@
         <v>179</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G30" s="9">
         <v>44.872</v>
@@ -4052,7 +3961,7 @@
         <v>41.88</v>
       </c>
       <c r="K30" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L30" s="5" t="s">
         <v>116</v>
@@ -4064,28 +3973,25 @@
         <v>44</v>
       </c>
       <c r="O30" s="8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="P30" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q30" t="s">
         <v>339</v>
       </c>
-      <c r="Q30" t="s">
+      <c r="R30" t="s">
         <v>340</v>
       </c>
-      <c r="R30" t="s">
-        <v>341</v>
-      </c>
-      <c r="S30" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T30" s="15" t="s">
-        <v>331</v>
-      </c>
-      <c r="U30" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S30" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="T30" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" s="11">
         <v>230</v>
       </c>
@@ -4102,7 +4008,7 @@
         <v>180</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G31" s="9">
         <v>75.536000000000001</v>
@@ -4117,7 +4023,7 @@
         <v>40.343000000000004</v>
       </c>
       <c r="K31" s="14" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L31" s="5" t="s">
         <v>119</v>
@@ -4129,25 +4035,22 @@
         <v>120</v>
       </c>
       <c r="O31" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="P31" t="s">
         <v>343</v>
       </c>
-      <c r="P31" t="s">
-        <v>344</v>
-      </c>
       <c r="Q31" t="s">
+        <v>345</v>
+      </c>
+      <c r="R31" t="s">
         <v>346</v>
       </c>
-      <c r="R31" t="s">
+      <c r="S31" s="18" t="s">
         <v>347</v>
       </c>
-      <c r="S31" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T31" s="18" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" s="11">
         <v>231</v>
       </c>
@@ -4158,13 +4061,13 @@
         <v>121</v>
       </c>
       <c r="D32" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>179</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G32" s="9">
         <v>87.554000000000002</v>
@@ -4179,7 +4082,7 @@
         <v>39.055999999999997</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L32" s="5" t="s">
         <v>122</v>
@@ -4191,25 +4094,22 @@
         <v>123</v>
       </c>
       <c r="O32" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="P32" t="s">
         <v>351</v>
       </c>
-      <c r="P32" t="s">
+      <c r="Q32" t="s">
         <v>352</v>
       </c>
-      <c r="Q32" t="s">
+      <c r="R32" t="s">
         <v>353</v>
       </c>
-      <c r="R32" t="s">
-        <v>354</v>
-      </c>
-      <c r="S32" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T32" s="18" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="S32" s="18" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" s="11">
         <v>232</v>
       </c>
@@ -4220,13 +4120,13 @@
         <v>124</v>
       </c>
       <c r="D33" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>180</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G33" s="9">
         <v>94.421000000000006</v>
@@ -4241,7 +4141,7 @@
         <v>41.631</v>
       </c>
       <c r="K33" s="14" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L33" s="5" t="s">
         <v>125</v>
@@ -4253,25 +4153,22 @@
         <v>123</v>
       </c>
       <c r="O33" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="P33" t="s">
         <v>355</v>
       </c>
-      <c r="P33" t="s">
+      <c r="Q33" t="s">
         <v>356</v>
       </c>
-      <c r="Q33" t="s">
+      <c r="R33" t="s">
         <v>357</v>
       </c>
-      <c r="R33" t="s">
-        <v>358</v>
-      </c>
-      <c r="S33" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T33" s="18" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="S33" s="18" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" s="11">
         <v>233</v>
       </c>
@@ -4288,7 +4185,7 @@
         <v>179</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G34" s="9">
         <v>44.444000000000003</v>
@@ -4315,25 +4212,22 @@
         <v>44</v>
       </c>
       <c r="O34" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="P34" t="s">
         <v>361</v>
       </c>
-      <c r="P34" t="s">
+      <c r="Q34" t="s">
         <v>362</v>
       </c>
-      <c r="Q34" t="s">
+      <c r="R34" t="s">
         <v>363</v>
       </c>
-      <c r="R34" t="s">
-        <v>364</v>
-      </c>
-      <c r="S34" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T34" s="18" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="S34" s="18" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" s="11">
         <v>234</v>
       </c>
@@ -4350,7 +4244,7 @@
         <v>180</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G35" s="9">
         <v>44.444000000000003</v>
@@ -4365,7 +4259,7 @@
         <v>43.161999999999999</v>
       </c>
       <c r="K35" s="14" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L35" s="5" t="s">
         <v>131</v>
@@ -4377,25 +4271,22 @@
         <v>44</v>
       </c>
       <c r="O35" s="8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P35" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q35" t="s">
         <v>370</v>
       </c>
-      <c r="Q35" t="s">
+      <c r="R35" t="s">
         <v>371</v>
       </c>
-      <c r="R35" t="s">
+      <c r="S35" s="18" t="s">
         <v>372</v>
       </c>
-      <c r="S35" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T35" s="18" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" s="11">
         <v>235</v>
       </c>
@@ -4412,7 +4303,7 @@
         <v>180</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G36" s="9">
         <v>45.298999999999999</v>
@@ -4427,7 +4318,7 @@
         <v>41.026000000000003</v>
       </c>
       <c r="K36" s="14" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L36" s="5" t="s">
         <v>134</v>
@@ -4439,25 +4330,22 @@
         <v>44</v>
       </c>
       <c r="O36" s="8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="P36" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q36" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="R36" t="s">
-        <v>378</v>
-      </c>
-      <c r="S36" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T36" s="15" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
+        <v>377</v>
+      </c>
+      <c r="S36" s="15" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" s="11">
         <v>236</v>
       </c>
@@ -4474,7 +4362,7 @@
         <v>179</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G37" s="9">
         <v>43.161999999999999</v>
@@ -4489,7 +4377,7 @@
         <v>42.308</v>
       </c>
       <c r="K37" s="14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L37" s="5" t="s">
         <v>137</v>
@@ -4501,25 +4389,22 @@
         <v>44</v>
       </c>
       <c r="O37" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="P37" t="s">
         <v>380</v>
       </c>
-      <c r="P37" t="s">
-        <v>381</v>
-      </c>
       <c r="Q37" t="s">
+        <v>382</v>
+      </c>
+      <c r="R37" t="s">
         <v>383</v>
       </c>
-      <c r="R37" t="s">
+      <c r="S37" s="18" t="s">
         <v>384</v>
       </c>
-      <c r="S37" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T37" s="18" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" s="11">
         <v>237</v>
       </c>
@@ -4536,7 +4421,7 @@
         <v>180</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G38" s="9">
         <v>43.59</v>
@@ -4551,7 +4436,7 @@
         <v>43.59</v>
       </c>
       <c r="K38" s="14" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L38" s="5" t="s">
         <v>140</v>
@@ -4563,25 +4448,22 @@
         <v>44</v>
       </c>
       <c r="O38" s="8" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P38" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q38" t="s">
         <v>389</v>
       </c>
-      <c r="Q38" t="s">
+      <c r="R38" t="s">
         <v>390</v>
       </c>
-      <c r="R38" t="s">
-        <v>391</v>
-      </c>
-      <c r="S38" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T38" s="15" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="S38" s="15" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" s="11">
         <v>238</v>
       </c>
@@ -4598,7 +4480,7 @@
         <v>180</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G39" s="9">
         <v>91.415999999999997</v>
@@ -4613,7 +4495,7 @@
         <v>41.201999999999998</v>
       </c>
       <c r="K39" s="14" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L39" s="5" t="s">
         <v>143</v>
@@ -4625,25 +4507,22 @@
         <v>76</v>
       </c>
       <c r="O39" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="P39" t="s">
         <v>393</v>
       </c>
-      <c r="P39" t="s">
-        <v>394</v>
-      </c>
       <c r="Q39" t="s">
+        <v>395</v>
+      </c>
+      <c r="R39" t="s">
         <v>396</v>
       </c>
-      <c r="R39" t="s">
-        <v>397</v>
-      </c>
-      <c r="S39" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T39" s="15" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="S39" s="15" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" s="11">
         <v>239</v>
       </c>
@@ -4660,7 +4539,7 @@
         <v>179</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G40" s="9">
         <v>89.27</v>
@@ -4675,7 +4554,7 @@
         <v>39.055999999999997</v>
       </c>
       <c r="K40" s="14" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L40" s="5" t="s">
         <v>146</v>
@@ -4687,25 +4566,22 @@
         <v>68</v>
       </c>
       <c r="O40" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="P40" t="s">
         <v>399</v>
       </c>
-      <c r="P40" t="s">
-        <v>400</v>
-      </c>
       <c r="Q40" t="s">
+        <v>401</v>
+      </c>
+      <c r="R40" t="s">
         <v>402</v>
       </c>
-      <c r="R40" t="s">
-        <v>403</v>
-      </c>
-      <c r="S40" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T40" s="18" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="S40" s="18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" s="11">
         <v>240</v>
       </c>
@@ -4722,7 +4598,7 @@
         <v>180</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G41" s="9">
         <v>45.725999999999999</v>
@@ -4737,7 +4613,7 @@
         <v>41.026000000000003</v>
       </c>
       <c r="K41" s="14" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="L41" s="5" t="s">
         <v>148</v>
@@ -4749,25 +4625,22 @@
         <v>44</v>
       </c>
       <c r="O41" s="8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="P41" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q41" t="s">
         <v>407</v>
       </c>
-      <c r="Q41" t="s">
+      <c r="R41" t="s">
         <v>408</v>
       </c>
-      <c r="R41" t="s">
-        <v>409</v>
-      </c>
-      <c r="S41" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T41" s="15" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="S41" s="15" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" s="11">
         <v>241</v>
       </c>
@@ -4784,7 +4657,7 @@
         <v>180</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G42" s="9">
         <v>73.819999999999993</v>
@@ -4799,7 +4672,7 @@
         <v>30.042999999999999</v>
       </c>
       <c r="K42" s="14" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L42" s="5" t="s">
         <v>151</v>
@@ -4811,25 +4684,22 @@
         <v>68</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P42" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q42" t="s">
+        <v>413</v>
+      </c>
+      <c r="R42" t="s">
         <v>414</v>
       </c>
-      <c r="R42" t="s">
-        <v>415</v>
-      </c>
-      <c r="S42" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T42" s="18" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="S42" s="18" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" s="11">
         <v>242</v>
       </c>
@@ -4846,7 +4716,7 @@
         <v>179</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G43" s="9">
         <v>92.703999999999994</v>
@@ -4861,7 +4731,7 @@
         <v>40.773000000000003</v>
       </c>
       <c r="K43" s="14" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L43" s="5" t="s">
         <v>155</v>
@@ -4873,25 +4743,22 @@
         <v>68</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P43" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="Q43" t="s">
+        <v>418</v>
+      </c>
+      <c r="R43" t="s">
         <v>419</v>
       </c>
-      <c r="R43" t="s">
-        <v>420</v>
-      </c>
-      <c r="S43" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T43" s="18" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="S43" s="18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" s="11">
         <v>243</v>
       </c>
@@ -4908,7 +4775,7 @@
         <v>180</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G44" s="9">
         <v>44.444000000000003</v>
@@ -4923,7 +4790,7 @@
         <v>41.453000000000003</v>
       </c>
       <c r="K44" s="14" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L44" s="5" t="s">
         <v>158</v>
@@ -4935,25 +4802,22 @@
         <v>44</v>
       </c>
       <c r="O44" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="P44" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Q44" t="s">
+        <v>425</v>
+      </c>
+      <c r="R44" t="s">
         <v>426</v>
       </c>
-      <c r="R44" t="s">
-        <v>427</v>
-      </c>
-      <c r="S44" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T44" s="15" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="S44" s="15" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" s="11">
         <v>244</v>
       </c>
@@ -4970,7 +4834,7 @@
         <v>180</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G45" s="9">
         <v>43.161999999999999</v>
@@ -4997,25 +4861,22 @@
         <v>44</v>
       </c>
       <c r="O45" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="P45" t="s">
         <v>428</v>
       </c>
-      <c r="P45" t="s">
-        <v>429</v>
-      </c>
       <c r="Q45" t="s">
+        <v>430</v>
+      </c>
+      <c r="R45" t="s">
         <v>431</v>
       </c>
-      <c r="R45" t="s">
-        <v>432</v>
-      </c>
-      <c r="S45" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T45" s="15" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="S45" s="15" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" s="11">
         <v>245</v>
       </c>
@@ -5032,7 +4893,7 @@
         <v>180</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G46" s="9">
         <v>97.424999999999997</v>
@@ -5047,7 +4908,7 @@
         <v>41.631</v>
       </c>
       <c r="K46" s="14" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="L46" s="5" t="s">
         <v>164</v>
@@ -5059,25 +4920,22 @@
         <v>68</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="P46" t="s">
+        <v>435</v>
+      </c>
+      <c r="Q46" t="s">
         <v>436</v>
       </c>
-      <c r="Q46" t="s">
+      <c r="R46" t="s">
         <v>437</v>
       </c>
-      <c r="R46" t="s">
-        <v>438</v>
-      </c>
-      <c r="S46" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T46" s="18" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="S46" s="18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" s="11">
         <v>246</v>
       </c>
@@ -5088,13 +4946,13 @@
         <v>165</v>
       </c>
       <c r="D47" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>179</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G47" s="9">
         <v>44.872</v>
@@ -5109,7 +4967,7 @@
         <v>42.308</v>
       </c>
       <c r="K47" s="14" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L47" s="5" t="s">
         <v>166</v>
@@ -5121,25 +4979,22 @@
         <v>44</v>
       </c>
       <c r="O47" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="P47" t="s">
         <v>439</v>
       </c>
-      <c r="P47" t="s">
-        <v>440</v>
-      </c>
       <c r="Q47" t="s">
+        <v>442</v>
+      </c>
+      <c r="R47" t="s">
         <v>443</v>
       </c>
-      <c r="R47" t="s">
+      <c r="S47" s="15" t="s">
         <v>444</v>
       </c>
-      <c r="S47" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T47" s="15" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" s="11">
         <v>247</v>
       </c>
@@ -5150,13 +5005,13 @@
         <v>167</v>
       </c>
       <c r="D48" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>179</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G48" s="9">
         <v>44.872</v>
@@ -5171,7 +5026,7 @@
         <v>42.308</v>
       </c>
       <c r="K48" s="14" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L48" s="5" t="s">
         <v>168</v>
@@ -5183,25 +5038,22 @@
         <v>44</v>
       </c>
       <c r="O48" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="P48" t="s">
         <v>447</v>
       </c>
-      <c r="P48" t="s">
-        <v>448</v>
-      </c>
       <c r="Q48" t="s">
+        <v>450</v>
+      </c>
+      <c r="R48" t="s">
         <v>451</v>
       </c>
-      <c r="R48" t="s">
-        <v>452</v>
-      </c>
-      <c r="S48" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T48" s="18" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="S48" s="18" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" s="11">
         <v>248</v>
       </c>
@@ -5218,7 +5070,7 @@
         <v>179</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G49" s="9">
         <v>44.444000000000003</v>
@@ -5233,7 +5085,7 @@
         <v>43.161999999999999</v>
       </c>
       <c r="K49" s="14" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L49" s="5" t="s">
         <v>171</v>
@@ -5245,25 +5097,22 @@
         <v>44</v>
       </c>
       <c r="O49" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="P49" t="s">
         <v>453</v>
       </c>
-      <c r="P49" t="s">
-        <v>454</v>
-      </c>
       <c r="Q49" t="s">
+        <v>455</v>
+      </c>
+      <c r="R49" t="s">
         <v>456</v>
       </c>
-      <c r="R49" t="s">
-        <v>457</v>
-      </c>
-      <c r="S49" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T49" s="18" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="S49" s="18" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" s="11">
         <v>249</v>
       </c>
@@ -5280,7 +5129,7 @@
         <v>180</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G50" s="9">
         <v>43.59</v>
@@ -5295,7 +5144,7 @@
         <v>44.017000000000003</v>
       </c>
       <c r="K50" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="L50" s="5" t="s">
         <v>174</v>
@@ -5307,25 +5156,22 @@
         <v>44</v>
       </c>
       <c r="O50" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="P50" t="s">
+        <v>461</v>
+      </c>
+      <c r="Q50" t="s">
         <v>462</v>
       </c>
-      <c r="Q50" t="s">
+      <c r="R50" t="s">
         <v>463</v>
       </c>
-      <c r="R50" t="s">
-        <v>464</v>
-      </c>
-      <c r="S50" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T50" s="15" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="S50" s="15" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" s="11">
         <v>250</v>
       </c>
@@ -5333,16 +5179,16 @@
         <v>180</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D51" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>179</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G51" s="9">
         <v>44.444000000000003</v>
@@ -5357,7 +5203,7 @@
         <v>43.161999999999999</v>
       </c>
       <c r="K51" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="L51" s="5" t="s">
         <v>175</v>
@@ -5369,25 +5215,22 @@
         <v>44</v>
       </c>
       <c r="O51" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="P51" t="s">
         <v>465</v>
       </c>
-      <c r="P51" t="s">
+      <c r="Q51" t="s">
         <v>466</v>
       </c>
-      <c r="Q51" t="s">
+      <c r="R51" t="s">
         <v>467</v>
       </c>
-      <c r="R51" t="s">
-        <v>468</v>
-      </c>
-      <c r="S51" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T51" s="18" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="S51" s="18" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" s="11">
         <v>251</v>
       </c>
@@ -5404,7 +5247,7 @@
         <v>180</v>
       </c>
       <c r="F52" s="16" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G52" s="9">
         <v>43.59</v>
@@ -5419,7 +5262,7 @@
         <v>41.88</v>
       </c>
       <c r="K52" s="14" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L52" s="5" t="s">
         <v>177</v>
@@ -5431,25 +5274,22 @@
         <v>44</v>
       </c>
       <c r="O52" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="P52" t="s">
         <v>471</v>
       </c>
-      <c r="P52" t="s">
-        <v>472</v>
-      </c>
       <c r="Q52" t="s">
+        <v>473</v>
+      </c>
+      <c r="R52" t="s">
         <v>474</v>
       </c>
-      <c r="R52" t="s">
-        <v>475</v>
-      </c>
-      <c r="S52" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T52" s="15" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="S52" s="15" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>311</v>
       </c>
@@ -5466,7 +5306,7 @@
         <v>179</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G53" s="13">
         <v>68.7</v>
@@ -5493,25 +5333,22 @@
         <v>22</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="P53" t="s">
         <v>197</v>
       </c>
       <c r="Q53" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R53" t="s">
-        <v>476</v>
-      </c>
-      <c r="S53" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T53" s="19" t="s">
+        <v>475</v>
+      </c>
+      <c r="S53" s="19" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>312</v>
       </c>
@@ -5528,7 +5365,7 @@
         <v>180</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G54" s="13">
         <v>46.4</v>
@@ -5543,7 +5380,7 @@
         <v>44.634999999999998</v>
       </c>
       <c r="K54" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L54" s="5" t="s">
         <v>25</v>
@@ -5555,25 +5392,22 @@
         <v>27</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="P54" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q54" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R54" t="s">
-        <v>476</v>
-      </c>
-      <c r="S54" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T54" s="18" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S54" s="18" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>313</v>
       </c>
@@ -5590,7 +5424,7 @@
         <v>179</v>
       </c>
       <c r="F55" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G55" s="13">
         <v>45.9</v>
@@ -5605,7 +5439,7 @@
         <v>43.347999999999999</v>
       </c>
       <c r="K55" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L55" s="5" t="s">
         <v>30</v>
@@ -5617,25 +5451,22 @@
         <v>31</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="P55" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>475</v>
+      </c>
+      <c r="R55" t="s">
+        <v>475</v>
+      </c>
+      <c r="S55" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="Q55" t="s">
-        <v>476</v>
-      </c>
-      <c r="R55" t="s">
-        <v>476</v>
-      </c>
-      <c r="S55" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T55" s="18" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>314</v>
       </c>
@@ -5652,7 +5483,7 @@
         <v>179</v>
       </c>
       <c r="F56" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G56" s="13">
         <v>44.9</v>
@@ -5667,7 +5498,7 @@
         <v>44.017000000000003</v>
       </c>
       <c r="K56" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L56" s="5" t="s">
         <v>34</v>
@@ -5679,25 +5510,22 @@
         <v>36</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="P56" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q56" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R56" t="s">
-        <v>476</v>
-      </c>
-      <c r="S56" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T56" s="18" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S56" s="18" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>315</v>
       </c>
@@ -5714,7 +5542,7 @@
         <v>179</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G57" s="13">
         <v>46.4</v>
@@ -5729,7 +5557,7 @@
         <v>43.777000000000001</v>
       </c>
       <c r="K57" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L57" s="5" t="s">
         <v>38</v>
@@ -5741,25 +5569,22 @@
         <v>31</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="P57" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q57" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R57" t="s">
-        <v>476</v>
-      </c>
-      <c r="S57" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T57" s="18" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S57" s="18" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
         <v>316</v>
       </c>
@@ -5776,7 +5601,7 @@
         <v>179</v>
       </c>
       <c r="F58" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G58" s="13">
         <v>43.2</v>
@@ -5791,7 +5616,7 @@
         <v>41.453000000000003</v>
       </c>
       <c r="K58" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L58" s="5" t="s">
         <v>41</v>
@@ -5803,25 +5628,22 @@
         <v>44</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="P58" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q58" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R58" t="s">
-        <v>476</v>
-      </c>
-      <c r="S58" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T58" s="18" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S58" s="18" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
         <v>317</v>
       </c>
@@ -5838,7 +5660,7 @@
         <v>180</v>
       </c>
       <c r="F59" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G59" s="13">
         <v>43.6</v>
@@ -5853,7 +5675,7 @@
         <v>41.453000000000003</v>
       </c>
       <c r="K59" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L59" s="5" t="s">
         <v>47</v>
@@ -5865,25 +5687,22 @@
         <v>44</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="P59" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q59" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R59" t="s">
-        <v>476</v>
-      </c>
-      <c r="S59" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T59" s="18" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S59" s="18" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
         <v>318</v>
       </c>
@@ -5900,7 +5719,7 @@
         <v>179</v>
       </c>
       <c r="F60" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G60" s="13">
         <v>44.9</v>
@@ -5915,7 +5734,7 @@
         <v>42.734999999999999</v>
       </c>
       <c r="K60" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L60" s="5" t="s">
         <v>50</v>
@@ -5927,25 +5746,22 @@
         <v>44</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P60" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q60" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R60" t="s">
-        <v>476</v>
-      </c>
-      <c r="S60" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T60" s="18" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S60" s="18" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
         <v>319</v>
       </c>
@@ -5962,7 +5778,7 @@
         <v>179</v>
       </c>
       <c r="F61" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G61" s="13">
         <v>71.7</v>
@@ -5977,7 +5793,7 @@
         <v>45.064</v>
       </c>
       <c r="K61" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L61" s="5" t="s">
         <v>54</v>
@@ -5989,25 +5805,22 @@
         <v>55</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="P61" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q61" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R61" t="s">
-        <v>476</v>
-      </c>
-      <c r="S61" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T61" s="18" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S61" s="18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
         <v>320</v>
       </c>
@@ -6024,7 +5837,7 @@
         <v>179</v>
       </c>
       <c r="F62" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G62" s="13">
         <v>35.700000000000003</v>
@@ -6039,7 +5852,7 @@
         <v>34.188000000000002</v>
       </c>
       <c r="K62" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L62" s="5" t="s">
         <v>58</v>
@@ -6051,25 +5864,22 @@
         <v>59</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="P62" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q62" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R62" t="s">
-        <v>476</v>
-      </c>
-      <c r="S62" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T62" s="18" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S62" s="18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
         <v>321</v>
       </c>
@@ -6086,7 +5896,7 @@
         <v>179</v>
       </c>
       <c r="F63" s="16" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G63" s="13">
         <v>89.7</v>
@@ -6101,7 +5911,7 @@
         <v>39.055999999999997</v>
       </c>
       <c r="K63" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L63" s="5" t="s">
         <v>67</v>
@@ -6113,25 +5923,22 @@
         <v>68</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="P63" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q63" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R63" t="s">
-        <v>476</v>
-      </c>
-      <c r="S63" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T63" s="18" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S63" s="18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
         <v>322</v>
       </c>
@@ -6148,7 +5955,7 @@
         <v>180</v>
       </c>
       <c r="F64" s="16" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G64" s="13">
         <v>29.63</v>
@@ -6163,7 +5970,7 @@
         <v>31.405000000000001</v>
       </c>
       <c r="K64" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L64" s="5" t="s">
         <v>71</v>
@@ -6175,25 +5982,22 @@
         <v>72</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="P64" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>475</v>
+      </c>
+      <c r="R64" t="s">
+        <v>475</v>
+      </c>
+      <c r="S64" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="P64" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>476</v>
-      </c>
-      <c r="R64" t="s">
-        <v>476</v>
-      </c>
-      <c r="S64" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T64" s="16" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>323</v>
       </c>
@@ -6210,7 +6014,7 @@
         <v>180</v>
       </c>
       <c r="F65" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G65" s="13">
         <v>90.6</v>
@@ -6225,7 +6029,7 @@
         <v>41.201999999999998</v>
       </c>
       <c r="K65" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L65" s="5" t="s">
         <v>75</v>
@@ -6237,25 +6041,22 @@
         <v>76</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="P65" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q65" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R65" t="s">
-        <v>476</v>
-      </c>
-      <c r="S65" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T65" s="3" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S65" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A66" s="11">
         <v>218</v>
       </c>
@@ -6272,7 +6073,7 @@
         <v>180</v>
       </c>
       <c r="F66" s="16" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G66" s="11">
         <v>43.2</v>
@@ -6287,7 +6088,7 @@
         <v>41.88</v>
       </c>
       <c r="K66" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L66" s="5" t="s">
         <v>79</v>
@@ -6299,25 +6100,22 @@
         <v>44</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="P66" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q66" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R66" t="s">
-        <v>476</v>
-      </c>
-      <c r="S66" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T66" s="18" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S66" s="18" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
         <v>324</v>
       </c>
@@ -6334,7 +6132,7 @@
         <v>179</v>
       </c>
       <c r="F67" s="16" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G67" s="11">
         <v>41.2</v>
@@ -6361,25 +6159,22 @@
         <v>64</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="P67" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q67" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R67" t="s">
-        <v>476</v>
-      </c>
-      <c r="S67" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T67" s="15" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S67" s="15" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
         <v>325</v>
       </c>
@@ -6396,7 +6191,7 @@
         <v>180</v>
       </c>
       <c r="F68" s="16" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G68" s="11">
         <v>100</v>
@@ -6423,25 +6218,22 @@
         <v>86</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P68" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q68" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R68" t="s">
-        <v>476</v>
-      </c>
-      <c r="S68" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T68" s="18" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S68" s="18" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
         <v>326</v>
       </c>
@@ -6458,7 +6250,7 @@
         <v>179</v>
       </c>
       <c r="F69" s="16" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G69" s="11">
         <v>93.1</v>
@@ -6473,7 +6265,7 @@
         <v>40.343000000000004</v>
       </c>
       <c r="K69" s="14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L69" s="5" t="s">
         <v>89</v>
@@ -6485,25 +6277,22 @@
         <v>90</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="P69" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q69" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R69" t="s">
-        <v>476</v>
-      </c>
-      <c r="S69" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T69" s="18" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S69" s="18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
         <v>327</v>
       </c>
@@ -6520,7 +6309,7 @@
         <v>179</v>
       </c>
       <c r="F70" s="16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G70" s="11">
         <v>91.8</v>
@@ -6535,7 +6324,7 @@
         <v>40.773000000000003</v>
       </c>
       <c r="K70" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L70" s="5" t="s">
         <v>93</v>
@@ -6547,25 +6336,22 @@
         <v>94</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P70" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q70" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R70" t="s">
-        <v>476</v>
-      </c>
-      <c r="S70" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T70" s="18" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S70" s="18" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
         <v>328</v>
       </c>
@@ -6582,7 +6368,7 @@
         <v>179</v>
       </c>
       <c r="F71" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G71" s="11">
         <v>87.1</v>
@@ -6597,7 +6383,7 @@
         <v>38.627000000000002</v>
       </c>
       <c r="K71" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L71" s="5" t="s">
         <v>97</v>
@@ -6609,25 +6395,22 @@
         <v>98</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P71" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q71" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R71" t="s">
-        <v>476</v>
-      </c>
-      <c r="S71" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T71" s="18" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S71" s="18" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
         <v>329</v>
       </c>
@@ -6644,7 +6427,7 @@
         <v>179</v>
       </c>
       <c r="F72" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G72" s="11">
         <v>92.3</v>
@@ -6659,7 +6442,7 @@
         <v>42.917999999999999</v>
       </c>
       <c r="K72" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L72" s="5" t="s">
         <v>101</v>
@@ -6671,25 +6454,22 @@
         <v>98</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="P72" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q72" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R72" t="s">
-        <v>476</v>
-      </c>
-      <c r="S72" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T72" s="18" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S72" s="18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
         <v>330</v>
       </c>
@@ -6706,7 +6486,7 @@
         <v>180</v>
       </c>
       <c r="F73" s="16" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G73" s="11">
         <v>41.9</v>
@@ -6721,7 +6501,7 @@
         <v>43.59</v>
       </c>
       <c r="K73" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L73" s="5" t="s">
         <v>104</v>
@@ -6733,25 +6513,22 @@
         <v>44</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="P73" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q73" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R73" t="s">
-        <v>476</v>
-      </c>
-      <c r="S73" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T73" s="15" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S73" s="15" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
         <v>331</v>
       </c>
@@ -6768,7 +6545,7 @@
         <v>179</v>
       </c>
       <c r="F74" s="16" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G74" s="11">
         <v>44.9</v>
@@ -6783,7 +6560,7 @@
         <v>43.161999999999999</v>
       </c>
       <c r="K74" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L74" s="5" t="s">
         <v>107</v>
@@ -6795,25 +6572,22 @@
         <v>44</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="P74" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Q74" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R74" t="s">
-        <v>476</v>
-      </c>
-      <c r="S74" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T74" s="15" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S74" s="15" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
         <v>332</v>
       </c>
@@ -6830,7 +6604,7 @@
         <v>179</v>
       </c>
       <c r="F75" s="16" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G75" s="11">
         <v>44.4</v>
@@ -6845,7 +6619,7 @@
         <v>42.308</v>
       </c>
       <c r="K75" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L75" s="5" t="s">
         <v>110</v>
@@ -6857,25 +6631,22 @@
         <v>44</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="P75" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Q75" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R75" t="s">
-        <v>476</v>
-      </c>
-      <c r="S75" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T75" s="15" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S75" s="15" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
         <v>333</v>
       </c>
@@ -6892,7 +6663,7 @@
         <v>179</v>
       </c>
       <c r="F76" s="16" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G76" s="11">
         <v>44.4</v>
@@ -6907,7 +6678,7 @@
         <v>43.161999999999999</v>
       </c>
       <c r="K76" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L76" s="5" t="s">
         <v>113</v>
@@ -6919,25 +6690,22 @@
         <v>44</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="P76" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q76" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R76" t="s">
-        <v>476</v>
-      </c>
-      <c r="S76" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T76" s="15" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S76" s="15" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
         <v>334</v>
       </c>
@@ -6954,7 +6722,7 @@
         <v>179</v>
       </c>
       <c r="F77" s="16" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G77" s="11">
         <v>44.9</v>
@@ -6969,7 +6737,7 @@
         <v>41.88</v>
       </c>
       <c r="K77" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L77" s="5" t="s">
         <v>116</v>
@@ -6981,25 +6749,22 @@
         <v>44</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="P77" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Q77" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R77" t="s">
-        <v>476</v>
-      </c>
-      <c r="S77" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T77" s="15" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S77" s="15" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
         <v>335</v>
       </c>
@@ -7016,7 +6781,7 @@
         <v>180</v>
       </c>
       <c r="F78" s="16" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G78" s="11">
         <v>75.5</v>
@@ -7031,7 +6796,7 @@
         <v>40.343000000000004</v>
       </c>
       <c r="K78" s="14" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L78" s="5" t="s">
         <v>119</v>
@@ -7043,25 +6808,22 @@
         <v>120</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="P78" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q78" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R78" t="s">
-        <v>476</v>
-      </c>
-      <c r="S78" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T78" s="18" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S78" s="18" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
         <v>336</v>
       </c>
@@ -7072,13 +6834,13 @@
         <v>121</v>
       </c>
       <c r="D79" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E79" s="5" t="s">
         <v>179</v>
       </c>
       <c r="F79" s="16" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G79" s="11">
         <v>87.6</v>
@@ -7093,7 +6855,7 @@
         <v>39.055999999999997</v>
       </c>
       <c r="K79" s="14" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L79" s="5" t="s">
         <v>122</v>
@@ -7105,25 +6867,22 @@
         <v>123</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="P79" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q79" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R79" t="s">
-        <v>476</v>
-      </c>
-      <c r="S79" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T79" s="18" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S79" s="18" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A80" s="4">
         <v>337</v>
       </c>
@@ -7134,13 +6893,13 @@
         <v>124</v>
       </c>
       <c r="D80" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E80" s="5" t="s">
         <v>180</v>
       </c>
       <c r="F80" s="16" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G80" s="11">
         <v>94.4</v>
@@ -7155,7 +6914,7 @@
         <v>41.631</v>
       </c>
       <c r="K80" s="14" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L80" s="5" t="s">
         <v>125</v>
@@ -7167,25 +6926,22 @@
         <v>123</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="P80" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Q80" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R80" t="s">
-        <v>476</v>
-      </c>
-      <c r="S80" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T80" s="18" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S80" s="18" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
         <v>338</v>
       </c>
@@ -7202,7 +6958,7 @@
         <v>179</v>
       </c>
       <c r="F81" s="16" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G81" s="11">
         <v>44.4</v>
@@ -7229,25 +6985,22 @@
         <v>44</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="P81" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Q81" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R81" t="s">
-        <v>476</v>
-      </c>
-      <c r="S81" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T81" s="18" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S81" s="18" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A82" s="4">
         <v>339</v>
       </c>
@@ -7264,7 +7017,7 @@
         <v>180</v>
       </c>
       <c r="F82" s="16" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G82" s="11">
         <v>44.4</v>
@@ -7279,7 +7032,7 @@
         <v>43.161999999999999</v>
       </c>
       <c r="K82" s="14" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L82" s="5" t="s">
         <v>131</v>
@@ -7291,25 +7044,22 @@
         <v>44</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="P82" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Q82" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R82" t="s">
-        <v>476</v>
-      </c>
-      <c r="S82" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T82" s="18" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S82" s="18" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A83" s="4">
         <v>340</v>
       </c>
@@ -7326,7 +7076,7 @@
         <v>180</v>
       </c>
       <c r="F83" s="16" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G83" s="11">
         <v>45.3</v>
@@ -7341,7 +7091,7 @@
         <v>41.026000000000003</v>
       </c>
       <c r="K83" s="14" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L83" s="5" t="s">
         <v>134</v>
@@ -7353,25 +7103,22 @@
         <v>44</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="P83" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q83" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R83" t="s">
-        <v>476</v>
-      </c>
-      <c r="S83" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T83" s="15" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S83" s="15" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
         <v>341</v>
       </c>
@@ -7388,7 +7135,7 @@
         <v>179</v>
       </c>
       <c r="F84" s="16" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G84" s="11">
         <v>43.2</v>
@@ -7403,7 +7150,7 @@
         <v>42.308</v>
       </c>
       <c r="K84" s="14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L84" s="5" t="s">
         <v>137</v>
@@ -7415,25 +7162,22 @@
         <v>44</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="P84" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Q84" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R84" t="s">
-        <v>476</v>
-      </c>
-      <c r="S84" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T84" s="18" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S84" s="18" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
         <v>342</v>
       </c>
@@ -7450,7 +7194,7 @@
         <v>180</v>
       </c>
       <c r="F85" s="16" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G85" s="11">
         <v>43.6</v>
@@ -7465,7 +7209,7 @@
         <v>43.59</v>
       </c>
       <c r="K85" s="14" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L85" s="5" t="s">
         <v>140</v>
@@ -7477,25 +7221,22 @@
         <v>44</v>
       </c>
       <c r="O85" s="6" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="P85" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="Q85" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R85" t="s">
-        <v>476</v>
-      </c>
-      <c r="S85" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T85" s="15" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S85" s="15" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A86" s="4">
         <v>343</v>
       </c>
@@ -7512,7 +7253,7 @@
         <v>180</v>
       </c>
       <c r="F86" s="16" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G86" s="11">
         <v>91.4</v>
@@ -7527,7 +7268,7 @@
         <v>41.201999999999998</v>
       </c>
       <c r="K86" s="14" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L86" s="5" t="s">
         <v>143</v>
@@ -7539,25 +7280,22 @@
         <v>76</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="P86" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="Q86" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R86" t="s">
-        <v>476</v>
-      </c>
-      <c r="S86" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T86" s="15" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S86" s="15" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A87" s="4">
         <v>344</v>
       </c>
@@ -7574,7 +7312,7 @@
         <v>179</v>
       </c>
       <c r="F87" s="16" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G87" s="11">
         <v>89.3</v>
@@ -7589,7 +7327,7 @@
         <v>39.055999999999997</v>
       </c>
       <c r="K87" s="14" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L87" s="5" t="s">
         <v>146</v>
@@ -7601,25 +7339,22 @@
         <v>68</v>
       </c>
       <c r="O87" s="6" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="P87" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q87" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R87" t="s">
-        <v>476</v>
-      </c>
-      <c r="S87" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T87" s="18" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S87" s="18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A88" s="4">
         <v>345</v>
       </c>
@@ -7636,7 +7371,7 @@
         <v>180</v>
       </c>
       <c r="F88" s="16" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G88" s="11">
         <v>45.7</v>
@@ -7651,7 +7386,7 @@
         <v>41.026000000000003</v>
       </c>
       <c r="K88" s="14" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="L88" s="5" t="s">
         <v>148</v>
@@ -7663,25 +7398,22 @@
         <v>44</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="P88" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q88" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R88" t="s">
-        <v>476</v>
-      </c>
-      <c r="S88" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T88" s="15" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S88" s="15" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A89" s="4">
         <v>346</v>
       </c>
@@ -7698,7 +7430,7 @@
         <v>180</v>
       </c>
       <c r="F89" s="16" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G89" s="11">
         <v>73.8</v>
@@ -7713,7 +7445,7 @@
         <v>30.042999999999999</v>
       </c>
       <c r="K89" s="14" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L89" s="5" t="s">
         <v>151</v>
@@ -7725,25 +7457,22 @@
         <v>68</v>
       </c>
       <c r="O89" s="6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="P89" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q89" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R89" t="s">
-        <v>476</v>
-      </c>
-      <c r="S89" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T89" s="18" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S89" s="18" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
         <v>347</v>
       </c>
@@ -7760,7 +7489,7 @@
         <v>179</v>
       </c>
       <c r="F90" s="16" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G90" s="11">
         <v>92.7</v>
@@ -7775,7 +7504,7 @@
         <v>40.773000000000003</v>
       </c>
       <c r="K90" s="14" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L90" s="5" t="s">
         <v>155</v>
@@ -7787,25 +7516,22 @@
         <v>68</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="P90" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="Q90" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R90" t="s">
-        <v>476</v>
-      </c>
-      <c r="S90" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T90" s="18" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S90" s="18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A91" s="4">
         <v>348</v>
       </c>
@@ -7822,7 +7548,7 @@
         <v>180</v>
       </c>
       <c r="F91" s="16" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G91" s="11">
         <v>44.4</v>
@@ -7837,7 +7563,7 @@
         <v>41.453000000000003</v>
       </c>
       <c r="K91" s="14" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L91" s="5" t="s">
         <v>158</v>
@@ -7849,25 +7575,22 @@
         <v>44</v>
       </c>
       <c r="O91" s="6" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="P91" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Q91" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R91" t="s">
-        <v>476</v>
-      </c>
-      <c r="S91" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T91" s="15" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S91" s="15" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A92" s="4">
         <v>349</v>
       </c>
@@ -7884,7 +7607,7 @@
         <v>180</v>
       </c>
       <c r="F92" s="16" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G92" s="11">
         <v>43.2</v>
@@ -7911,25 +7634,22 @@
         <v>44</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="P92" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Q92" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R92" t="s">
-        <v>476</v>
-      </c>
-      <c r="S92" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T92" s="15" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S92" s="15" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A93" s="4">
         <v>350</v>
       </c>
@@ -7946,7 +7666,7 @@
         <v>180</v>
       </c>
       <c r="F93" s="16" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G93" s="11">
         <v>97.4</v>
@@ -7961,7 +7681,7 @@
         <v>41.631</v>
       </c>
       <c r="K93" s="14" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="L93" s="5" t="s">
         <v>164</v>
@@ -7973,25 +7693,22 @@
         <v>68</v>
       </c>
       <c r="O93" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="P93" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q93" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R93" t="s">
-        <v>476</v>
-      </c>
-      <c r="S93" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T93" s="18" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S93" s="18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A94" s="4">
         <v>351</v>
       </c>
@@ -8002,13 +7719,13 @@
         <v>165</v>
       </c>
       <c r="D94" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E94" s="5" t="s">
         <v>179</v>
       </c>
       <c r="F94" s="16" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G94" s="11">
         <v>44.9</v>
@@ -8023,7 +7740,7 @@
         <v>42.308</v>
       </c>
       <c r="K94" s="14" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L94" s="5" t="s">
         <v>166</v>
@@ -8035,25 +7752,22 @@
         <v>44</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="P94" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="Q94" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R94" t="s">
-        <v>476</v>
-      </c>
-      <c r="S94" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T94" s="15" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S94" s="15" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A95" s="4">
         <v>352</v>
       </c>
@@ -8064,13 +7778,13 @@
         <v>167</v>
       </c>
       <c r="D95" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E95" s="5" t="s">
         <v>179</v>
       </c>
       <c r="F95" s="16" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G95" s="11">
         <v>44.9</v>
@@ -8085,7 +7799,7 @@
         <v>42.308</v>
       </c>
       <c r="K95" s="14" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L95" s="5" t="s">
         <v>168</v>
@@ -8097,25 +7811,22 @@
         <v>44</v>
       </c>
       <c r="O95" s="6" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="P95" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Q95" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R95" t="s">
-        <v>476</v>
-      </c>
-      <c r="S95" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T95" s="18" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S95" s="18" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A96" s="4">
         <v>353</v>
       </c>
@@ -8132,7 +7843,7 @@
         <v>179</v>
       </c>
       <c r="F96" s="16" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G96" s="11">
         <v>44.4</v>
@@ -8147,7 +7858,7 @@
         <v>43.161999999999999</v>
       </c>
       <c r="K96" s="14" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L96" s="5" t="s">
         <v>171</v>
@@ -8159,25 +7870,22 @@
         <v>44</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="P96" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Q96" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R96" t="s">
-        <v>476</v>
-      </c>
-      <c r="S96" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T96" s="18" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S96" s="18" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A97" s="4">
         <v>354</v>
       </c>
@@ -8194,7 +7902,7 @@
         <v>180</v>
       </c>
       <c r="F97" s="16" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G97" s="11">
         <v>43.6</v>
@@ -8209,7 +7917,7 @@
         <v>44.017000000000003</v>
       </c>
       <c r="K97" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="L97" s="5" t="s">
         <v>174</v>
@@ -8221,25 +7929,22 @@
         <v>44</v>
       </c>
       <c r="O97" s="6" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="P97" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="Q97" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R97" t="s">
-        <v>476</v>
-      </c>
-      <c r="S97" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T97" s="15" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S97" s="15" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A98" s="4">
         <v>355</v>
       </c>
@@ -8247,16 +7952,16 @@
         <v>179</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D98" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E98" s="5" t="s">
         <v>179</v>
       </c>
       <c r="F98" s="16" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G98" s="11">
         <v>44.4</v>
@@ -8271,7 +7976,7 @@
         <v>43.161999999999999</v>
       </c>
       <c r="K98" s="14" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="L98" s="5" t="s">
         <v>175</v>
@@ -8283,25 +7988,22 @@
         <v>44</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="P98" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q98" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R98" t="s">
-        <v>476</v>
-      </c>
-      <c r="S98" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T98" s="18" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S98" s="18" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A99" s="4">
         <v>356</v>
       </c>
@@ -8318,7 +8020,7 @@
         <v>180</v>
       </c>
       <c r="F99" s="16" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G99" s="11">
         <v>43.6</v>
@@ -8333,7 +8035,7 @@
         <v>41.88</v>
       </c>
       <c r="K99" s="14" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L99" s="5" t="s">
         <v>177</v>
@@ -8345,25 +8047,22 @@
         <v>44</v>
       </c>
       <c r="O99" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="P99" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="Q99" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R99" t="s">
-        <v>476</v>
-      </c>
-      <c r="S99" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="T99" s="15" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.2">
+        <v>475</v>
+      </c>
+      <c r="S99" s="15" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B100" s="4"/>
       <c r="C100" s="6"/>
       <c r="D100" s="5"/>
@@ -8375,8 +8074,7 @@
       <c r="M100" s="6"/>
       <c r="N100" s="6"/>
       <c r="O100" s="17"/>
-      <c r="S100" s="6"/>
-      <c r="T100" s="18"/>
+      <c r="S100" s="18"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -8384,74 +8082,74 @@
     <hyperlink ref="N16" r:id="rId2" xr:uid="{0446FBC7-AC3A-7E45-8322-C0A86EDC27D7}"/>
     <hyperlink ref="N7" r:id="rId3" xr:uid="{A5FE866C-873A-514C-96DB-8D78C2980865}"/>
     <hyperlink ref="N9" r:id="rId4" xr:uid="{BA6A1D43-E996-BC4D-A21F-D35B39E76930}"/>
-    <hyperlink ref="T2" r:id="rId5" display="https://doi.org/10.1099/vir.0.039479-0" xr:uid="{1FC1C0B3-0B4E-564C-BE13-4D1A36865A26}"/>
-    <hyperlink ref="T3" r:id="rId6" display="https://doi.org/10.1099/vir.0.039479-0" xr:uid="{7E8420F1-4894-1245-AF55-98547EC66965}"/>
-    <hyperlink ref="T5" r:id="rId7" display="https://doi.org/10.3201/eid2103.141351" xr:uid="{205CD9A0-09E6-234C-9B2D-CF6FB355BD1B}"/>
-    <hyperlink ref="T4" r:id="rId8" display="https://doi.org/10.1099/vir.0.039479-0" xr:uid="{83AAF5C5-A6A0-AD4E-BC44-6AD8E3D13004}"/>
-    <hyperlink ref="T6" r:id="rId9" display="https://doi.org/10.1371/journal.pntd.0003147" xr:uid="{DE1171F5-F8B6-8845-BCA4-7867DFAF8516}"/>
-    <hyperlink ref="T7" r:id="rId10" display="https://doi.org/10.1371/journal.pntd.0003147" xr:uid="{6D1597D7-ED34-D44A-BD3E-D1E835DF440B}"/>
-    <hyperlink ref="T8" r:id="rId11" display="https://doi.org/10.1099/vir.0.2008/002253-0" xr:uid="{EDB5BC55-950C-B441-ACF0-480C10DF0467}"/>
-    <hyperlink ref="T9" r:id="rId12" display="https://doi.org/10.1099/vir.0.2008/002253-0" xr:uid="{E036CF19-6ED7-3442-AE5A-7C7C8292D31D}"/>
-    <hyperlink ref="T10" r:id="rId13" display="https://doi.org/10.1099/jgv.0.000899" xr:uid="{0BCAA4EC-92EC-C54A-B528-9CB63C056F4D}"/>
-    <hyperlink ref="T11" r:id="rId14" display="https://doi.org/10.1099/jgv.0.000899" xr:uid="{8BFD61D2-447C-1443-9034-5E57F0D1ECCA}"/>
-    <hyperlink ref="T12" r:id="rId15" display="https://doi.org/10.1099/0022-1317-76-3-559" xr:uid="{CDD231AA-DB83-E24C-85A8-CE21CA15A9C7}"/>
-    <hyperlink ref="T13" r:id="rId16" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{DE3B0EB0-DD68-8648-941F-7C894E50B13B}"/>
-    <hyperlink ref="T14" r:id="rId17" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{CAF7B8C6-1F2F-AD46-8411-B2515AD269DC}"/>
-    <hyperlink ref="T15" r:id="rId18" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{0A98F58D-6FD2-7F48-BE41-E8E37EB6F7B0}"/>
-    <hyperlink ref="T16" r:id="rId19" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{CCF4B0DE-9E28-6842-8147-926EF5924319}"/>
-    <hyperlink ref="T19" r:id="rId20" display="https://doi.org/10.1186/1743-422x-4-41" xr:uid="{B751E9E0-3208-E04B-84B1-422264FCB246}"/>
-    <hyperlink ref="T21" r:id="rId21" display="https://doi.org/10.1099/0022-1317-70-5-1281" xr:uid="{C4EE5BDD-9719-2248-8E13-4D07F1A7D306}"/>
-    <hyperlink ref="T22" r:id="rId22" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{7FA86F3A-8860-1347-9357-F27046C00576}"/>
-    <hyperlink ref="T23" r:id="rId23" display="https://doi.org/10.1128/jvi.02641-12" xr:uid="{5D92561E-65E8-5D49-BFD5-3E9BE5E8E35F}"/>
-    <hyperlink ref="T24" r:id="rId24" display="https://doi.org/10.1099/vir.0.82643-0" xr:uid="{56EC2F4D-5E90-FB4B-8F14-4D7A2FEF4D8E}"/>
-    <hyperlink ref="T25" r:id="rId25" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{D65D600E-54C7-9F4B-A0D5-1ACD9ADDC9AC}"/>
-    <hyperlink ref="T31" r:id="rId26" display="https://doi.org/10.1128/genomea.00433-14" xr:uid="{0768C8CE-2E0C-814A-AE24-B8B9BAE1A279}"/>
-    <hyperlink ref="T32" r:id="rId27" display="https://doi.org/10.1099/vir.0.82643-0" xr:uid="{E71E3954-715E-B848-A4D4-2AFE0BC615AA}"/>
-    <hyperlink ref="T33" r:id="rId28" display="https://doi.org/10.1016/j.meegid.2013.08.015" xr:uid="{59DE2F6F-C9C0-E04D-B6A3-2604F07FA90F}"/>
-    <hyperlink ref="T34" r:id="rId29" display="https://doi.org/10.1099/0022-1317-77-8-1761" xr:uid="{E0F0ABB1-863C-1845-97B3-CAE3C316B44E}"/>
-    <hyperlink ref="T35" r:id="rId30" display="https://doi.org/10.1186/1743-422x-8-136" xr:uid="{DDF1DF5B-8006-834C-BDB9-00CD21A3D619}"/>
-    <hyperlink ref="T37" r:id="rId31" display="https://doi.org/10.3201/eid1605.100170" xr:uid="{AE246D4C-515C-F843-A6B3-70C4E1321D38}"/>
-    <hyperlink ref="T40" r:id="rId32" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{F8E96B7A-EC0A-F442-8CF1-D82ADFB0E4C8}"/>
-    <hyperlink ref="T42" r:id="rId33" display="https://doi.org/10.1099/vir.0.82643-0" xr:uid="{82282806-B5AF-6E43-87A1-F7C7BF3EBF5E}"/>
-    <hyperlink ref="T43" r:id="rId34" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{52C9430D-042A-B342-B09A-BBE6C608758E}"/>
-    <hyperlink ref="T46" r:id="rId35" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{86ECDB88-0063-4C4B-BB94-7D8EA56B2110}"/>
-    <hyperlink ref="T48" r:id="rId36" display="https://doi.org/10.1093/nar/10.12.3703" xr:uid="{5A431033-0DE5-D141-AEBF-DC63A43FAD07}"/>
-    <hyperlink ref="T49" r:id="rId37" display="https://doi.org/10.1099/0022-1317-77-8-1761" xr:uid="{0300F76E-094E-6741-B867-E68FBD059BBA}"/>
-    <hyperlink ref="T51" r:id="rId38" display="https://doi.org/10.1016/j.virusres.2010.01.005" xr:uid="{87A8978B-9A26-F64B-99D9-FBADB7B682FF}"/>
+    <hyperlink ref="S2" r:id="rId5" display="https://doi.org/10.1099/vir.0.039479-0" xr:uid="{1FC1C0B3-0B4E-564C-BE13-4D1A36865A26}"/>
+    <hyperlink ref="S3" r:id="rId6" display="https://doi.org/10.1099/vir.0.039479-0" xr:uid="{7E8420F1-4894-1245-AF55-98547EC66965}"/>
+    <hyperlink ref="S5" r:id="rId7" display="https://doi.org/10.3201/eid2103.141351" xr:uid="{205CD9A0-09E6-234C-9B2D-CF6FB355BD1B}"/>
+    <hyperlink ref="S4" r:id="rId8" display="https://doi.org/10.1099/vir.0.039479-0" xr:uid="{83AAF5C5-A6A0-AD4E-BC44-6AD8E3D13004}"/>
+    <hyperlink ref="S6" r:id="rId9" display="https://doi.org/10.1371/journal.pntd.0003147" xr:uid="{DE1171F5-F8B6-8845-BCA4-7867DFAF8516}"/>
+    <hyperlink ref="S7" r:id="rId10" display="https://doi.org/10.1371/journal.pntd.0003147" xr:uid="{6D1597D7-ED34-D44A-BD3E-D1E835DF440B}"/>
+    <hyperlink ref="S8" r:id="rId11" display="https://doi.org/10.1099/vir.0.2008/002253-0" xr:uid="{EDB5BC55-950C-B441-ACF0-480C10DF0467}"/>
+    <hyperlink ref="S9" r:id="rId12" display="https://doi.org/10.1099/vir.0.2008/002253-0" xr:uid="{E036CF19-6ED7-3442-AE5A-7C7C8292D31D}"/>
+    <hyperlink ref="S10" r:id="rId13" display="https://doi.org/10.1099/jgv.0.000899" xr:uid="{0BCAA4EC-92EC-C54A-B528-9CB63C056F4D}"/>
+    <hyperlink ref="S11" r:id="rId14" display="https://doi.org/10.1099/jgv.0.000899" xr:uid="{8BFD61D2-447C-1443-9034-5E57F0D1ECCA}"/>
+    <hyperlink ref="S12" r:id="rId15" display="https://doi.org/10.1099/0022-1317-76-3-559" xr:uid="{CDD231AA-DB83-E24C-85A8-CE21CA15A9C7}"/>
+    <hyperlink ref="S13" r:id="rId16" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{DE3B0EB0-DD68-8648-941F-7C894E50B13B}"/>
+    <hyperlink ref="S14" r:id="rId17" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{CAF7B8C6-1F2F-AD46-8411-B2515AD269DC}"/>
+    <hyperlink ref="S15" r:id="rId18" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{0A98F58D-6FD2-7F48-BE41-E8E37EB6F7B0}"/>
+    <hyperlink ref="S16" r:id="rId19" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{CCF4B0DE-9E28-6842-8147-926EF5924319}"/>
+    <hyperlink ref="S19" r:id="rId20" display="https://doi.org/10.1186/1743-422x-4-41" xr:uid="{B751E9E0-3208-E04B-84B1-422264FCB246}"/>
+    <hyperlink ref="S21" r:id="rId21" display="https://doi.org/10.1099/0022-1317-70-5-1281" xr:uid="{C4EE5BDD-9719-2248-8E13-4D07F1A7D306}"/>
+    <hyperlink ref="S22" r:id="rId22" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{7FA86F3A-8860-1347-9357-F27046C00576}"/>
+    <hyperlink ref="S23" r:id="rId23" display="https://doi.org/10.1128/jvi.02641-12" xr:uid="{5D92561E-65E8-5D49-BFD5-3E9BE5E8E35F}"/>
+    <hyperlink ref="S24" r:id="rId24" display="https://doi.org/10.1099/vir.0.82643-0" xr:uid="{56EC2F4D-5E90-FB4B-8F14-4D7A2FEF4D8E}"/>
+    <hyperlink ref="S25" r:id="rId25" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{D65D600E-54C7-9F4B-A0D5-1ACD9ADDC9AC}"/>
+    <hyperlink ref="S31" r:id="rId26" display="https://doi.org/10.1128/genomea.00433-14" xr:uid="{0768C8CE-2E0C-814A-AE24-B8B9BAE1A279}"/>
+    <hyperlink ref="S32" r:id="rId27" display="https://doi.org/10.1099/vir.0.82643-0" xr:uid="{E71E3954-715E-B848-A4D4-2AFE0BC615AA}"/>
+    <hyperlink ref="S33" r:id="rId28" display="https://doi.org/10.1016/j.meegid.2013.08.015" xr:uid="{59DE2F6F-C9C0-E04D-B6A3-2604F07FA90F}"/>
+    <hyperlink ref="S34" r:id="rId29" display="https://doi.org/10.1099/0022-1317-77-8-1761" xr:uid="{E0F0ABB1-863C-1845-97B3-CAE3C316B44E}"/>
+    <hyperlink ref="S35" r:id="rId30" display="https://doi.org/10.1186/1743-422x-8-136" xr:uid="{DDF1DF5B-8006-834C-BDB9-00CD21A3D619}"/>
+    <hyperlink ref="S37" r:id="rId31" display="https://doi.org/10.3201/eid1605.100170" xr:uid="{AE246D4C-515C-F843-A6B3-70C4E1321D38}"/>
+    <hyperlink ref="S40" r:id="rId32" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{F8E96B7A-EC0A-F442-8CF1-D82ADFB0E4C8}"/>
+    <hyperlink ref="S42" r:id="rId33" display="https://doi.org/10.1099/vir.0.82643-0" xr:uid="{82282806-B5AF-6E43-87A1-F7C7BF3EBF5E}"/>
+    <hyperlink ref="S43" r:id="rId34" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{52C9430D-042A-B342-B09A-BBE6C608758E}"/>
+    <hyperlink ref="S46" r:id="rId35" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{86ECDB88-0063-4C4B-BB94-7D8EA56B2110}"/>
+    <hyperlink ref="S48" r:id="rId36" display="https://doi.org/10.1093/nar/10.12.3703" xr:uid="{5A431033-0DE5-D141-AEBF-DC63A43FAD07}"/>
+    <hyperlink ref="S49" r:id="rId37" display="https://doi.org/10.1099/0022-1317-77-8-1761" xr:uid="{0300F76E-094E-6741-B867-E68FBD059BBA}"/>
+    <hyperlink ref="S51" r:id="rId38" display="https://doi.org/10.1016/j.virusres.2010.01.005" xr:uid="{87A8978B-9A26-F64B-99D9-FBADB7B682FF}"/>
     <hyperlink ref="N55" r:id="rId39" xr:uid="{10A0BCF8-AEB1-1B46-B2CE-6C256BBD3942}"/>
     <hyperlink ref="N57" r:id="rId40" xr:uid="{3CA4732B-239E-7D41-AB89-87ACB7B93273}"/>
-    <hyperlink ref="T53" r:id="rId41" display="https://doi.org/10.3201/eid2103.141351" xr:uid="{009C4C97-58AF-9946-8F84-D5C60E95E72F}"/>
-    <hyperlink ref="T54" r:id="rId42" display="https://doi.org/10.1371/journal.pntd.0003147" xr:uid="{15CEC5C1-0F6A-7140-9C03-D0DAE559DB26}"/>
-    <hyperlink ref="T55" r:id="rId43" display="https://doi.org/10.1371/journal.pntd.0003147" xr:uid="{5CE5270F-EC33-474A-BB10-EE057CC3EC2B}"/>
-    <hyperlink ref="T56" r:id="rId44" display="https://doi.org/10.1099/vir.0.2008/002253-0" xr:uid="{45524AA7-4F6E-7B47-A6F1-8907AFFB8F10}"/>
-    <hyperlink ref="T57" r:id="rId45" display="https://doi.org/10.1099/vir.0.2008/002253-0" xr:uid="{EF5984E9-66A5-F44D-941C-53527423E6EB}"/>
-    <hyperlink ref="T58" r:id="rId46" display="https://doi.org/10.1099/jgv.0.000899" xr:uid="{509DF018-44FB-6C47-A0AD-6914D4229B36}"/>
-    <hyperlink ref="T59" r:id="rId47" display="https://doi.org/10.1099/jgv.0.000899" xr:uid="{346CBD4D-38E9-424B-8CCC-8948CFB03493}"/>
-    <hyperlink ref="T60" r:id="rId48" display="https://doi.org/10.1099/0022-1317-76-3-559" xr:uid="{10B54180-88BB-FF4F-B6EF-03A957C6EE4A}"/>
-    <hyperlink ref="T61" r:id="rId49" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{D4E1F029-4F28-9D42-A79B-0CDDA1471487}"/>
-    <hyperlink ref="T62" r:id="rId50" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{B06DB2F8-4505-1A4B-9201-60E605A63EFE}"/>
+    <hyperlink ref="S53" r:id="rId41" display="https://doi.org/10.3201/eid2103.141351" xr:uid="{009C4C97-58AF-9946-8F84-D5C60E95E72F}"/>
+    <hyperlink ref="S54" r:id="rId42" display="https://doi.org/10.1371/journal.pntd.0003147" xr:uid="{15CEC5C1-0F6A-7140-9C03-D0DAE559DB26}"/>
+    <hyperlink ref="S55" r:id="rId43" display="https://doi.org/10.1371/journal.pntd.0003147" xr:uid="{5CE5270F-EC33-474A-BB10-EE057CC3EC2B}"/>
+    <hyperlink ref="S56" r:id="rId44" display="https://doi.org/10.1099/vir.0.2008/002253-0" xr:uid="{45524AA7-4F6E-7B47-A6F1-8907AFFB8F10}"/>
+    <hyperlink ref="S57" r:id="rId45" display="https://doi.org/10.1099/vir.0.2008/002253-0" xr:uid="{EF5984E9-66A5-F44D-941C-53527423E6EB}"/>
+    <hyperlink ref="S58" r:id="rId46" display="https://doi.org/10.1099/jgv.0.000899" xr:uid="{509DF018-44FB-6C47-A0AD-6914D4229B36}"/>
+    <hyperlink ref="S59" r:id="rId47" display="https://doi.org/10.1099/jgv.0.000899" xr:uid="{346CBD4D-38E9-424B-8CCC-8948CFB03493}"/>
+    <hyperlink ref="S60" r:id="rId48" display="https://doi.org/10.1099/0022-1317-76-3-559" xr:uid="{10B54180-88BB-FF4F-B6EF-03A957C6EE4A}"/>
+    <hyperlink ref="S61" r:id="rId49" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{D4E1F029-4F28-9D42-A79B-0CDDA1471487}"/>
+    <hyperlink ref="S62" r:id="rId50" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{B06DB2F8-4505-1A4B-9201-60E605A63EFE}"/>
     <hyperlink ref="N93" r:id="rId51" xr:uid="{7FE7F194-C09A-574E-BE74-F4E81AD7FFF5}"/>
     <hyperlink ref="N63" r:id="rId52" xr:uid="{CB711DF7-5322-D54A-BA29-1DDCF6151C40}"/>
-    <hyperlink ref="T63" r:id="rId53" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{08548F24-8157-AE46-A175-77528DA0A0A4}"/>
-    <hyperlink ref="T66" r:id="rId54" display="https://doi.org/10.1186/1743-422x-4-41" xr:uid="{31AC6C3C-F115-DC48-9F78-2B8DEA16C354}"/>
-    <hyperlink ref="T68" r:id="rId55" display="https://doi.org/10.1099/0022-1317-70-5-1281" xr:uid="{00D47566-5D13-DC48-B364-50DC5E6831AB}"/>
-    <hyperlink ref="T69" r:id="rId56" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{A77BD633-C53B-8E46-B8EF-5979F3A59232}"/>
-    <hyperlink ref="T70" r:id="rId57" display="https://doi.org/10.1128/jvi.02641-12" xr:uid="{10730BFF-28F4-4944-8E2A-DC716922F1ED}"/>
-    <hyperlink ref="T71" r:id="rId58" display="https://doi.org/10.1099/vir.0.82643-0" xr:uid="{C6004447-C0A4-7249-85B5-E778A92467A2}"/>
-    <hyperlink ref="T72" r:id="rId59" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{1B5B279A-063E-FA40-B104-E6E417EE51EF}"/>
-    <hyperlink ref="T78" r:id="rId60" display="https://doi.org/10.1128/genomea.00433-14" xr:uid="{25969CD1-9E46-ED41-9FDD-D5D0DEB024BD}"/>
-    <hyperlink ref="T79" r:id="rId61" display="https://doi.org/10.1099/vir.0.82643-0" xr:uid="{1D52E481-FA6F-5147-9200-8D039D7D1E19}"/>
-    <hyperlink ref="T80" r:id="rId62" display="https://doi.org/10.1016/j.meegid.2013.08.015" xr:uid="{9C7F644E-AEE8-444B-B765-A5D28D9C1E22}"/>
-    <hyperlink ref="T81" r:id="rId63" display="https://doi.org/10.1099/0022-1317-77-8-1761" xr:uid="{7E7290E9-BE7E-6246-BB6B-7B1148424649}"/>
-    <hyperlink ref="T82" r:id="rId64" display="https://doi.org/10.1186/1743-422x-8-136" xr:uid="{532B70F0-D57F-BE4C-944A-0DEDAB091A2B}"/>
-    <hyperlink ref="T84" r:id="rId65" display="https://doi.org/10.3201/eid1605.100170" xr:uid="{A84133BE-A867-1642-B381-702562FB5E65}"/>
-    <hyperlink ref="T87" r:id="rId66" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{CB915F5A-0D22-6442-85C3-4833BED57DE8}"/>
-    <hyperlink ref="T89" r:id="rId67" display="https://doi.org/10.1099/vir.0.82643-0" xr:uid="{59E5B753-EB77-E94A-979E-0162D91A85E4}"/>
-    <hyperlink ref="T90" r:id="rId68" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{B572BDAA-B076-144B-8F95-B88E2B3882EE}"/>
-    <hyperlink ref="T93" r:id="rId69" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{D9385357-0295-DF46-AB46-6064AE7B1581}"/>
-    <hyperlink ref="T95" r:id="rId70" display="https://doi.org/10.1093/nar/10.12.3703" xr:uid="{236F059D-614F-8C41-AD11-9F78AA81D16F}"/>
-    <hyperlink ref="T96" r:id="rId71" display="https://doi.org/10.1099/0022-1317-77-8-1761" xr:uid="{EEFABEE2-C1E4-CD44-9195-C7746FFEA3B5}"/>
-    <hyperlink ref="T98" r:id="rId72" display="https://doi.org/10.1016/j.virusres.2010.01.005" xr:uid="{E28C4795-51C4-804E-8149-5639A6C414AF}"/>
+    <hyperlink ref="S63" r:id="rId53" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{08548F24-8157-AE46-A175-77528DA0A0A4}"/>
+    <hyperlink ref="S66" r:id="rId54" display="https://doi.org/10.1186/1743-422x-4-41" xr:uid="{31AC6C3C-F115-DC48-9F78-2B8DEA16C354}"/>
+    <hyperlink ref="S68" r:id="rId55" display="https://doi.org/10.1099/0022-1317-70-5-1281" xr:uid="{00D47566-5D13-DC48-B364-50DC5E6831AB}"/>
+    <hyperlink ref="S69" r:id="rId56" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{A77BD633-C53B-8E46-B8EF-5979F3A59232}"/>
+    <hyperlink ref="S70" r:id="rId57" display="https://doi.org/10.1128/jvi.02641-12" xr:uid="{10730BFF-28F4-4944-8E2A-DC716922F1ED}"/>
+    <hyperlink ref="S71" r:id="rId58" display="https://doi.org/10.1099/vir.0.82643-0" xr:uid="{C6004447-C0A4-7249-85B5-E778A92467A2}"/>
+    <hyperlink ref="S72" r:id="rId59" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{1B5B279A-063E-FA40-B104-E6E417EE51EF}"/>
+    <hyperlink ref="S78" r:id="rId60" display="https://doi.org/10.1128/genomea.00433-14" xr:uid="{25969CD1-9E46-ED41-9FDD-D5D0DEB024BD}"/>
+    <hyperlink ref="S79" r:id="rId61" display="https://doi.org/10.1099/vir.0.82643-0" xr:uid="{1D52E481-FA6F-5147-9200-8D039D7D1E19}"/>
+    <hyperlink ref="S80" r:id="rId62" display="https://doi.org/10.1016/j.meegid.2013.08.015" xr:uid="{9C7F644E-AEE8-444B-B765-A5D28D9C1E22}"/>
+    <hyperlink ref="S81" r:id="rId63" display="https://doi.org/10.1099/0022-1317-77-8-1761" xr:uid="{7E7290E9-BE7E-6246-BB6B-7B1148424649}"/>
+    <hyperlink ref="S82" r:id="rId64" display="https://doi.org/10.1186/1743-422x-8-136" xr:uid="{532B70F0-D57F-BE4C-944A-0DEDAB091A2B}"/>
+    <hyperlink ref="S84" r:id="rId65" display="https://doi.org/10.3201/eid1605.100170" xr:uid="{A84133BE-A867-1642-B381-702562FB5E65}"/>
+    <hyperlink ref="S87" r:id="rId66" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{CB915F5A-0D22-6442-85C3-4833BED57DE8}"/>
+    <hyperlink ref="S89" r:id="rId67" display="https://doi.org/10.1099/vir.0.82643-0" xr:uid="{59E5B753-EB77-E94A-979E-0162D91A85E4}"/>
+    <hyperlink ref="S90" r:id="rId68" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{B572BDAA-B076-144B-8F95-B88E2B3882EE}"/>
+    <hyperlink ref="S93" r:id="rId69" display="https://doi.org/10.1371/journal.ppat.1009315" xr:uid="{D9385357-0295-DF46-AB46-6064AE7B1581}"/>
+    <hyperlink ref="S95" r:id="rId70" display="https://doi.org/10.1093/nar/10.12.3703" xr:uid="{236F059D-614F-8C41-AD11-9F78AA81D16F}"/>
+    <hyperlink ref="S96" r:id="rId71" display="https://doi.org/10.1099/0022-1317-77-8-1761" xr:uid="{EEFABEE2-C1E4-CD44-9195-C7746FFEA3B5}"/>
+    <hyperlink ref="S98" r:id="rId72" display="https://doi.org/10.1016/j.virusres.2010.01.005" xr:uid="{E28C4795-51C4-804E-8149-5639A6C414AF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
